--- a/Самарканд_Хуршед ака 2.xlsx
+++ b/Самарканд_Хуршед ака 2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shakhrizodaisoeva/Desktop/Bot data/Prays list/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1095591-7AAA-BB46-B4F7-AA5D60E9E8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{500F7C30-F908-2648-B1C2-B53C4BDEFFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="37">
   <si>
     <t>МНН</t>
   </si>
@@ -138,6 +138,16 @@
   </si>
   <si>
     <t>«ZEISS PHARMACEUTICALS PVT.LTD»</t>
+  </si>
+  <si>
+    <t>Семпер р-р. для инф 200 мл №1</t>
+  </si>
+  <si>
+    <t>Sorbitol, sodium lactate, sodium chloride,
+potassium chloride, calcium chloride, magnesium chloride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СП ООО "Reka Med Farm" </t>
   </si>
 </sst>
 </file>
@@ -339,7 +349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -371,6 +381,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -412,7 +459,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -507,11 +554,20 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="36">
@@ -948,7 +1004,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:M25"/>
+  <dimension ref="A3:M26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="25"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -987,16 +1043,16 @@
     </row>
     <row r="6" spans="1:11" ht="49" customHeight="1">
       <c r="B6" s="16"/>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
       <c r="K6" s="16"/>
     </row>
     <row r="7" spans="1:11" ht="49" customHeight="1">
@@ -1081,11 +1137,11 @@
         <v>90000</v>
       </c>
       <c r="G10" s="26">
-        <f t="shared" ref="G10:G15" si="0">F10*(1+$G$8%)</f>
+        <f t="shared" ref="G10:G16" si="0">F10*(1+$G$8%)</f>
         <v>103499.99999999999</v>
       </c>
       <c r="H10" s="26">
-        <f t="shared" ref="H10:H15" si="1">+G10*1.12</f>
+        <f t="shared" ref="H10:H16" si="1">+G10*1.12</f>
         <v>115920</v>
       </c>
       <c r="I10" s="27">
@@ -1266,45 +1322,78 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-    </row>
-    <row r="18" spans="2:11" ht="130" customHeight="1">
-      <c r="B18" s="32" t="s">
+    <row r="16" spans="1:11" ht="40">
+      <c r="B16" s="22">
+        <v>7</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="24">
+        <v>28</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="26">
+        <v>40000</v>
+      </c>
+      <c r="G16" s="26">
+        <f t="shared" si="0"/>
+        <v>46000</v>
+      </c>
+      <c r="H16" s="26">
+        <f t="shared" si="1"/>
+        <v>51520.000000000007</v>
+      </c>
+      <c r="I16" s="27">
+        <v>46661</v>
+      </c>
+      <c r="J16" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="33"/>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="2:11" ht="130" customHeight="1">
+      <c r="B19" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="2:11">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="36"/>
     </row>
     <row r="20" spans="2:11">
-      <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1316,26 +1405,38 @@
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="2:11">
-      <c r="K21" s="15"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
     </row>
     <row r="22" spans="2:11">
-      <c r="K22" s="21"/>
+      <c r="K22" s="15"/>
     </row>
     <row r="23" spans="2:11">
       <c r="K23" s="21"/>
     </row>
     <row r="24" spans="2:11">
-      <c r="K24" s="15"/>
-    </row>
-    <row r="25" spans="2:11" ht="25" customHeight="1">
-      <c r="K25" s="1"/>
+      <c r="K24" s="21"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="K25" s="15"/>
+    </row>
+    <row r="26" spans="2:11" ht="25" customHeight="1">
+      <c r="K26" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="B9:K13" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="4">
     <mergeCell ref="J8:K8"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:K18"/>
+    <mergeCell ref="B19:K19"/>
     <mergeCell ref="C6:J6"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
